--- a/output/tables/pfratio_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/pfratio_12h_by_treatment_patient_level.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">Time Since Randomisation (hours)
 </t>
@@ -22,6 +22,9 @@
   </si>
   <si>
     <t xml:space="preserve">Welch Two Sample t-test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
   <si>
     <t xml:space="preserve">Patients
@@ -102,6 +105,47 @@
   </si>
   <si>
     <t xml:space="preserve">27.84 (8.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean Difference
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.33, 1.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.13, 1.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.39, 1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.49, 2.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.30, 2.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.65, 3.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.19, 5.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.67, 6.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.61, 6.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.91, 6.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.29, 4.53</t>
   </si>
   <si>
     <t xml:space="preserve">p-value
@@ -550,6 +594,8 @@
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="NA" customHeight="1">
@@ -557,16 +603,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -577,12 +629,18 @@
         <v>58</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="7" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -594,12 +652,18 @@
         <v>59</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="8" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="8" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -611,12 +675,18 @@
         <v>57</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="8" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="8" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -628,12 +698,18 @@
         <v>55</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="8" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="8" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -645,12 +721,18 @@
         <v>53</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="8" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -662,12 +744,18 @@
         <v>52</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="8" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -679,12 +767,18 @@
         <v>51</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="8" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -696,13 +790,19 @@
         <v>49</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -713,12 +813,18 @@
         <v>49</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="8" t="n">
+        <v>-0.69</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -730,12 +836,18 @@
         <v>40</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="8" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -747,12 +859,18 @@
         <v>38</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="9" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -772,28 +890,64 @@
       <c r="E13" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="F13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="F14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="NA" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
+  <mergeCells count="3">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/output/tables/pfratio_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/pfratio_12h_by_treatment_patient_level.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Time Since Randomisation (hours)
 </t>
@@ -32,79 +32,79 @@
   </si>
   <si>
     <t xml:space="preserve">Conservative
-N = 29
+N = 31
 </t>
   </si>
   <si>
-    <t xml:space="preserve">23.56 (11.12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.59 (8.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.76 (8.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.51 (9.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.77 (7.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.56 (9.13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.61 (10.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.07 (10.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.12 (10.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.61 (12.18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.96 (10.57)</t>
+    <t xml:space="preserve">23.22 (10.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.24 (8.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.68 (8.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.21 (9.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.61 (8.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.92 (9.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.75 (10.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.24 (10.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.18 (10.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.77 (11.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.72 (10.36)</t>
   </si>
   <si>
     <t xml:space="preserve">Usual care
-N = 30
+N = 35
 </t>
   </si>
   <si>
-    <t xml:space="preserve">28.14 (10.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.28 (8.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.43 (9.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.79 (9.48)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.26 (9.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.67 (10.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.20 (12.92)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.26 (12.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.81 (13.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.32 (10.27)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.84 (8.90)</t>
+    <t xml:space="preserve">26.74 (10.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.07 (8.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.47 (9.03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.17 (9.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.75 (9.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.02 (10.45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.71 (12.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.38 (11.78)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.07 (14.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.93 (10.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.89 (12.44)</t>
   </si>
   <si>
     <t xml:space="preserve">Mean Difference
@@ -115,44 +115,41 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">-10.33, 1.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.13, 1.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.39, 1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.49, 2.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.30, 2.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.65, 3.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.19, 5.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.67, 6.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.61, 6.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.91, 6.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.29, 4.53</t>
+    <t xml:space="preserve">-8.95, 1.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.08, 2.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.21, 1.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.83, 2.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.67, 1.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.22, 3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.04, 4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.06, 4.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.75, 2.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.74, 4.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.56, 3.22</t>
   </si>
   <si>
     <t xml:space="preserve">p-value
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;0.9</t>
   </si>
 </sst>
 </file>
@@ -626,7 +623,7 @@
         <v>-12</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>6</v>
@@ -635,13 +632,13 @@
         <v>18</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>-4.58</v>
+        <v>-3.52</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -649,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>7</v>
@@ -658,13 +655,13 @@
         <v>19</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-2.7</v>
+        <v>-1.83</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -672,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -681,13 +678,13 @@
         <v>20</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-3.67</v>
+        <v>-2.79</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>33</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -695,7 +692,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
@@ -704,7 +701,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-2.28</v>
+        <v>-1.96</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>34</v>
@@ -718,7 +715,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>10</v>
@@ -727,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-2.49</v>
+        <v>-3.13</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -741,7 +738,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>11</v>
@@ -750,7 +747,7 @@
         <v>23</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-2.11</v>
+        <v>-2.1</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>36</v>
@@ -764,7 +761,7 @@
         <v>60</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>12</v>
@@ -773,13 +770,13 @@
         <v>24</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -787,7 +784,7 @@
         <v>72</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>13</v>
@@ -796,13 +793,13 @@
         <v>25</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.19</v>
+        <v>-1.14</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>43</v>
+      <c r="G9" s="8" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -810,7 +807,7 @@
         <v>84</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>14</v>
@@ -819,13 +816,13 @@
         <v>26</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.69</v>
+        <v>-3.89</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -833,7 +830,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>15</v>
@@ -842,13 +839,13 @@
         <v>27</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-0.72</v>
+        <v>-2.16</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -856,7 +853,7 @@
         <v>108</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>16</v>
@@ -865,13 +862,13 @@
         <v>28</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-1.88</v>
+        <v>-4.17</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">

--- a/output/tables/pfratio_12h_by_treatment_patient_level.xlsx
+++ b/output/tables/pfratio_12h_by_treatment_patient_level.xlsx
@@ -18,55 +18,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Mean (SD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Welch Two Sample t-test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
-  </si>
-  <si>
     <t xml:space="preserve">Patients
 </t>
   </si>
   <si>
     <t xml:space="preserve">Conservative
-N = 31
+N = 30
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.22 (10.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.24 (8.36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.68 (8.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.21 (9.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.61 (8.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.92 (9.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.75 (10.51)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.24 (10.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.18 (10.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.77 (11.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.72 (10.36)</t>
   </si>
   <si>
     <t xml:space="preserve">Usual care
@@ -74,39 +32,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">26.74 (10.86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.07 (8.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.47 (9.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.17 (9.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.75 (9.38)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.02 (10.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.71 (12.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.38 (11.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.07 (14.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.93 (10.36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.89 (12.44)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mean Difference
 </t>
   </si>
@@ -115,41 +40,116 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">-8.95, 1.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.08, 2.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.21, 1.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.83, 2.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.67, 1.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.22, 3.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.04, 4.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.06, 4.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.75, 2.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.74, 4.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.56, 3.22</t>
-  </si>
-  <si>
     <t xml:space="preserve">p-value
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.72 (10.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.70 (10.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.41, 1.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.92 (8.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.52 (9.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.90, 1.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.27 (8.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.83 (9.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.03, 0.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.02 (7.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.61 (9.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.06, 0.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.37 (8.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.92 (9.49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.17, 1.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.45 (9.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.14 (10.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.84, 2.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.38 (10.54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.56 (12.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.29, 3.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.93 (10.35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.12 (11.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.12, 4.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.18 (10.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.58 (14.23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.17, 3.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.77 (11.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.74 (10.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.49, 4.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.72 (10.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.30 (8.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.74, 3.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean (SD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welch Two Sample t-test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
 </sst>
 </file>
@@ -600,22 +600,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="G1" s="6" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -626,19 +626,19 @@
         <v>64</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>-3.52</v>
+        <v>-3.97</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -649,19 +649,19 @@
         <v>65</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-1.83</v>
+        <v>-2.6</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -669,22 +669,22 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-2.79</v>
+        <v>-3.56</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -692,22 +692,22 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-1.96</v>
+        <v>-3.59</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -715,22 +715,22 @@
         <v>36</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-3.13</v>
+        <v>-3.55</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -738,22 +738,22 @@
         <v>48</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-2.1</v>
+        <v>-2.68</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -761,19 +761,19 @@
         <v>60</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-1.96</v>
+        <v>-2.17</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>0.5</v>
@@ -784,19 +784,19 @@
         <v>72</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-1.14</v>
+        <v>-1.19</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>0.7</v>
@@ -810,16 +810,16 @@
         <v>56</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-3.89</v>
+        <v>-3.4</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>0.3</v>
@@ -833,16 +833,16 @@
         <v>47</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-2.16</v>
+        <v>-1.97</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>0.5</v>
@@ -856,88 +856,88 @@
         <v>40</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-4.17</v>
+        <v>-2.58</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
